--- a/Nuevos DeepWins/Problem2_Checkerboard6x6/Res/Comparativa_6_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem2_Checkerboard6x6/Res/Comparativa_6_Neuronas.xlsx
@@ -581,42 +581,42 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.24867</v>
+        <v>0.215997</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1790729879</v>
+        <v>1790729834</v>
       </c>
       <c r="E2" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
         <v>200000</v>
       </c>
       <c r="G2" t="n">
-        <v>0.518828</v>
+        <v>0.615104</v>
       </c>
       <c r="H2" t="n">
-        <v>0.469105</v>
+        <v>0.636822</v>
       </c>
       <c r="I2" t="n">
-        <v>0.492715</v>
+        <v>0.625775</v>
       </c>
       <c r="J2" t="n">
-        <v>0.252005</v>
+        <v>0.218337</v>
       </c>
       <c r="K2" t="n">
-        <v>0.439153</v>
+        <v>0.581281</v>
       </c>
       <c r="L2" t="n">
-        <v>0.44385</v>
+        <v>0.631016</v>
       </c>
       <c r="M2" t="n">
-        <v>0.441489</v>
+        <v>0.605128</v>
       </c>
       <c r="N2" t="n">
         <v>0.2</v>
@@ -652,23 +652,23 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_13.txt</t>
+          <t>_2_6_1_1790729834_2.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z2" t="n">
         <v>6</v>
       </c>
       <c r="AA2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -682,7 +682,7 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.248748</v>
+        <v>0.225568</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -699,25 +699,25 @@
         <v>200000</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5286459999999999</v>
+        <v>0.580071</v>
       </c>
       <c r="H3" t="n">
-        <v>0.51198</v>
+        <v>0.411097</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5201789999999999</v>
+        <v>0.481181</v>
       </c>
       <c r="J3" t="n">
-        <v>0.252082</v>
+        <v>0.229596</v>
       </c>
       <c r="K3" t="n">
-        <v>0.439394</v>
+        <v>0.564516</v>
       </c>
       <c r="L3" t="n">
-        <v>0.465241</v>
+        <v>0.374332</v>
       </c>
       <c r="M3" t="n">
-        <v>0.451948</v>
+        <v>0.450161</v>
       </c>
       <c r="N3" t="n">
         <v>0.2</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_16.txt</t>
+          <t>_2_3_3_1_1790729879_7.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -783,42 +783,42 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.243843</v>
+        <v>0.241098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1790729879</v>
+        <v>1790729834</v>
       </c>
       <c r="E4" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
         <v>200000</v>
       </c>
       <c r="G4" t="n">
-        <v>0.552113</v>
+        <v>0.551343</v>
       </c>
       <c r="H4" t="n">
-        <v>0.247163</v>
+        <v>0.440101</v>
       </c>
       <c r="I4" t="n">
-        <v>0.341463</v>
+        <v>0.489481</v>
       </c>
       <c r="J4" t="n">
-        <v>0.24836</v>
+        <v>0.243971</v>
       </c>
       <c r="K4" t="n">
-        <v>0.460674</v>
+        <v>0.458333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.219251</v>
+        <v>0.352941</v>
       </c>
       <c r="M4" t="n">
-        <v>0.297101</v>
+        <v>0.398792</v>
       </c>
       <c r="N4" t="n">
         <v>0.2</v>
@@ -854,23 +854,23 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_4.txt</t>
+          <t>_2_6_1_1790729834_4.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z4" t="n">
         <v>6</v>
       </c>
       <c r="AA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -884,7 +884,7 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.215997</v>
+        <v>0.23057</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
         <v>200000</v>
       </c>
       <c r="G5" t="n">
-        <v>0.615104</v>
+        <v>0.60503</v>
       </c>
       <c r="H5" t="n">
-        <v>0.636822</v>
+        <v>0.515763</v>
       </c>
       <c r="I5" t="n">
-        <v>0.625775</v>
+        <v>0.556841</v>
       </c>
       <c r="J5" t="n">
-        <v>0.218337</v>
+        <v>0.243836</v>
       </c>
       <c r="K5" t="n">
-        <v>0.581281</v>
+        <v>0.489933</v>
       </c>
       <c r="L5" t="n">
-        <v>0.631016</v>
+        <v>0.390374</v>
       </c>
       <c r="M5" t="n">
-        <v>0.605128</v>
+        <v>0.434524</v>
       </c>
       <c r="N5" t="n">
         <v>0.2</v>
@@ -955,7 +955,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_2.txt</t>
+          <t>_2_6_1_1790729834_1.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -985,7 +985,7 @@
         <v>0.1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.247883</v>
+        <v>0.226233</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
         <v>200000</v>
       </c>
       <c r="G6" t="n">
-        <v>0.535433</v>
+        <v>0.577256</v>
       </c>
       <c r="H6" t="n">
-        <v>0.428752</v>
+        <v>0.588903</v>
       </c>
       <c r="I6" t="n">
-        <v>0.47619</v>
+        <v>0.583021</v>
       </c>
       <c r="J6" t="n">
-        <v>0.251054</v>
+        <v>0.228458</v>
       </c>
       <c r="K6" t="n">
-        <v>0.432258</v>
+        <v>0.514286</v>
       </c>
       <c r="L6" t="n">
-        <v>0.358289</v>
+        <v>0.5775400000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.391813</v>
+        <v>0.544081</v>
       </c>
       <c r="N6" t="n">
         <v>0.2</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_11.txt</t>
+          <t>_2_3_3_1_1790729879_15.txt</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1086,42 +1086,42 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2189</v>
+        <v>0.248769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1790729834</v>
+        <v>1790729879</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="F7" t="n">
         <v>200000</v>
       </c>
       <c r="G7" t="n">
-        <v>0.637363</v>
+        <v>0.534247</v>
       </c>
       <c r="H7" t="n">
-        <v>0.58512</v>
+        <v>0.491803</v>
       </c>
       <c r="I7" t="n">
-        <v>0.610125</v>
+        <v>0.512147</v>
       </c>
       <c r="J7" t="n">
-        <v>0.220178</v>
+        <v>0.252621</v>
       </c>
       <c r="K7" t="n">
-        <v>0.605556</v>
+        <v>0.433155</v>
       </c>
       <c r="L7" t="n">
-        <v>0.582888</v>
+        <v>0.433155</v>
       </c>
       <c r="M7" t="n">
-        <v>0.594005</v>
+        <v>0.433155</v>
       </c>
       <c r="N7" t="n">
         <v>0.2</v>
@@ -1157,23 +1157,23 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_15.txt</t>
+          <t>_2_3_3_1_1790729879_8.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z7" t="n">
         <v>6</v>
       </c>
       <c r="AA7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1187,7 +1187,7 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.218953</v>
+        <v>0.2189</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1204,25 +1204,25 @@
         <v>200000</v>
       </c>
       <c r="G8" t="n">
-        <v>0.649371</v>
+        <v>0.637363</v>
       </c>
       <c r="H8" t="n">
-        <v>0.520807</v>
+        <v>0.58512</v>
       </c>
       <c r="I8" t="n">
-        <v>0.578027</v>
+        <v>0.610125</v>
       </c>
       <c r="J8" t="n">
-        <v>0.221643</v>
+        <v>0.220178</v>
       </c>
       <c r="K8" t="n">
-        <v>0.608696</v>
+        <v>0.605556</v>
       </c>
       <c r="L8" t="n">
-        <v>0.524064</v>
+        <v>0.582888</v>
       </c>
       <c r="M8" t="n">
-        <v>0.563218</v>
+        <v>0.594005</v>
       </c>
       <c r="N8" t="n">
         <v>0.2</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_10.txt</t>
+          <t>_2_6_1_1790729834_15.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1288,7 +1288,7 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.245617</v>
+        <v>0.246505</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1305,25 +1305,25 @@
         <v>200000</v>
       </c>
       <c r="G9" t="n">
-        <v>0.560794</v>
+        <v>0.487075</v>
       </c>
       <c r="H9" t="n">
-        <v>0.284994</v>
+        <v>0.45145</v>
       </c>
       <c r="I9" t="n">
-        <v>0.377926</v>
+        <v>0.468586</v>
       </c>
       <c r="J9" t="n">
-        <v>0.250612</v>
+        <v>0.252228</v>
       </c>
       <c r="K9" t="n">
-        <v>0.480392</v>
+        <v>0.425641</v>
       </c>
       <c r="L9" t="n">
-        <v>0.262032</v>
+        <v>0.44385</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3391</v>
+        <v>0.434555</v>
       </c>
       <c r="N9" t="n">
         <v>0.2</v>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_6.txt</t>
+          <t>_2_3_3_1_1790729879_9.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1389,7 +1389,7 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.234669</v>
+        <v>0.245234</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1406,25 +1406,25 @@
         <v>200000</v>
       </c>
       <c r="G10" t="n">
-        <v>0.544811</v>
+        <v>0.535664</v>
       </c>
       <c r="H10" t="n">
-        <v>0.291299</v>
+        <v>0.482976</v>
       </c>
       <c r="I10" t="n">
-        <v>0.379622</v>
+        <v>0.507958</v>
       </c>
       <c r="J10" t="n">
-        <v>0.238642</v>
+        <v>0.251466</v>
       </c>
       <c r="K10" t="n">
-        <v>0.524272</v>
+        <v>0.478261</v>
       </c>
       <c r="L10" t="n">
-        <v>0.28877</v>
+        <v>0.470588</v>
       </c>
       <c r="M10" t="n">
-        <v>0.372414</v>
+        <v>0.474394</v>
       </c>
       <c r="N10" t="n">
         <v>0.2</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_3.txt</t>
+          <t>_2_3_3_1_1790729879_12.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1490,7 +1490,7 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.219263</v>
+        <v>0.225188</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1507,25 +1507,25 @@
         <v>200000</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6411480000000001</v>
+        <v>0.605882</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5069360000000001</v>
+        <v>0.519546</v>
       </c>
       <c r="I11" t="n">
-        <v>0.566197</v>
+        <v>0.559403</v>
       </c>
       <c r="J11" t="n">
-        <v>0.221056</v>
+        <v>0.22671</v>
       </c>
       <c r="K11" t="n">
-        <v>0.615385</v>
+        <v>0.579268</v>
       </c>
       <c r="L11" t="n">
-        <v>0.513369</v>
+        <v>0.5080209999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.559767</v>
+        <v>0.541311</v>
       </c>
       <c r="N11" t="n">
         <v>0.2</v>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_12.txt</t>
+          <t>_2_6_1_1790729834_13.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1591,42 +1591,42 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.205486</v>
+        <v>0.248484</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1790729834</v>
+        <v>1790729879</v>
       </c>
       <c r="E12" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="F12" t="n">
         <v>200000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.663142</v>
+        <v>0.537037</v>
       </c>
       <c r="H12" t="n">
-        <v>0.553594</v>
+        <v>0.43884</v>
       </c>
       <c r="I12" t="n">
-        <v>0.603436</v>
+        <v>0.482998</v>
       </c>
       <c r="J12" t="n">
-        <v>0.215537</v>
+        <v>0.252834</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5962730000000001</v>
+        <v>0.460606</v>
       </c>
       <c r="L12" t="n">
-        <v>0.513369</v>
+        <v>0.406417</v>
       </c>
       <c r="M12" t="n">
-        <v>0.551724</v>
+        <v>0.431818</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
@@ -1662,23 +1662,23 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_0.txt</t>
+          <t>_2_3_3_1_1790729879_14.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z12" t="n">
         <v>6</v>
       </c>
       <c r="AA12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1692,42 +1692,42 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.215203</v>
+        <v>0.24867</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1790729834</v>
+        <v>1790729879</v>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
         <v>200000</v>
       </c>
       <c r="G13" t="n">
-        <v>0.609524</v>
+        <v>0.518828</v>
       </c>
       <c r="H13" t="n">
-        <v>0.645649</v>
+        <v>0.469105</v>
       </c>
       <c r="I13" t="n">
-        <v>0.627067</v>
+        <v>0.492715</v>
       </c>
       <c r="J13" t="n">
-        <v>0.217863</v>
+        <v>0.252005</v>
       </c>
       <c r="K13" t="n">
-        <v>0.566667</v>
+        <v>0.439153</v>
       </c>
       <c r="L13" t="n">
-        <v>0.636364</v>
+        <v>0.44385</v>
       </c>
       <c r="M13" t="n">
-        <v>0.599496</v>
+        <v>0.441489</v>
       </c>
       <c r="N13" t="n">
         <v>0.2</v>
@@ -1763,23 +1763,23 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_11.txt</t>
+          <t>_2_3_3_1_1790729879_13.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z13" t="n">
         <v>6</v>
       </c>
       <c r="AA13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1793,7 +1793,7 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.246505</v>
+        <v>0.248883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1810,25 +1810,25 @@
         <v>200000</v>
       </c>
       <c r="G14" t="n">
-        <v>0.487075</v>
+        <v>0.527512</v>
       </c>
       <c r="H14" t="n">
-        <v>0.45145</v>
+        <v>0.5561160000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.468586</v>
+        <v>0.541436</v>
       </c>
       <c r="J14" t="n">
-        <v>0.252228</v>
+        <v>0.251582</v>
       </c>
       <c r="K14" t="n">
-        <v>0.425641</v>
+        <v>0.464789</v>
       </c>
       <c r="L14" t="n">
-        <v>0.44385</v>
+        <v>0.529412</v>
       </c>
       <c r="M14" t="n">
-        <v>0.434555</v>
+        <v>0.495</v>
       </c>
       <c r="N14" t="n">
         <v>0.2</v>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_9.txt</t>
+          <t>_2_3_3_1_1790729879_5.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1894,42 +1894,42 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.248498</v>
+        <v>0.239137</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1790729879</v>
+        <v>1790729834</v>
       </c>
       <c r="E15" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="F15" t="n">
         <v>200000</v>
       </c>
       <c r="G15" t="n">
-        <v>0.553468</v>
+        <v>0.546995</v>
       </c>
       <c r="H15" t="n">
-        <v>0.482976</v>
+        <v>0.447667</v>
       </c>
       <c r="I15" t="n">
-        <v>0.515825</v>
+        <v>0.492372</v>
       </c>
       <c r="J15" t="n">
-        <v>0.251417</v>
+        <v>0.242724</v>
       </c>
       <c r="K15" t="n">
-        <v>0.505952</v>
+        <v>0.503401</v>
       </c>
       <c r="L15" t="n">
-        <v>0.454545</v>
+        <v>0.395722</v>
       </c>
       <c r="M15" t="n">
-        <v>0.478873</v>
+        <v>0.443114</v>
       </c>
       <c r="N15" t="n">
         <v>0.2</v>
@@ -1965,23 +1965,23 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_10.txt</t>
+          <t>_2_6_1_1790729834_9.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z15" t="n">
         <v>6</v>
       </c>
       <c r="AA15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -1995,7 +1995,7 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.215825</v>
+        <v>0.223623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2012,25 +2012,25 @@
         <v>200000</v>
       </c>
       <c r="G16" t="n">
-        <v>0.644947</v>
+        <v>0.589641</v>
       </c>
       <c r="H16" t="n">
-        <v>0.611602</v>
+        <v>0.559899</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6278319999999999</v>
+        <v>0.574386</v>
       </c>
       <c r="J16" t="n">
-        <v>0.217323</v>
+        <v>0.225489</v>
       </c>
       <c r="K16" t="n">
-        <v>0.618785</v>
+        <v>0.5625</v>
       </c>
       <c r="L16" t="n">
-        <v>0.59893</v>
+        <v>0.529412</v>
       </c>
       <c r="M16" t="n">
-        <v>0.608696</v>
+        <v>0.545455</v>
       </c>
       <c r="N16" t="n">
         <v>0.2</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_7.txt</t>
+          <t>_2_6_1_1790729834_17.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2096,7 +2096,7 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.216022</v>
+        <v>0.214512</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2113,25 +2113,25 @@
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.613609</v>
+        <v>0.633152</v>
       </c>
       <c r="H17" t="n">
-        <v>0.636822</v>
+        <v>0.587642</v>
       </c>
       <c r="I17" t="n">
-        <v>0.625</v>
+        <v>0.609549</v>
       </c>
       <c r="J17" t="n">
-        <v>0.218002</v>
+        <v>0.216096</v>
       </c>
       <c r="K17" t="n">
-        <v>0.576355</v>
+        <v>0.596591</v>
       </c>
       <c r="L17" t="n">
-        <v>0.625668</v>
+        <v>0.561497</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6</v>
+        <v>0.578512</v>
       </c>
       <c r="N17" t="n">
         <v>0.2</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_16.txt</t>
+          <t>_2_6_1_1790729834_6.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2197,7 +2197,7 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.225188</v>
+        <v>0.205486</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2214,25 +2214,25 @@
         <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.605882</v>
+        <v>0.663142</v>
       </c>
       <c r="H18" t="n">
-        <v>0.519546</v>
+        <v>0.553594</v>
       </c>
       <c r="I18" t="n">
-        <v>0.559403</v>
+        <v>0.603436</v>
       </c>
       <c r="J18" t="n">
-        <v>0.22671</v>
+        <v>0.215537</v>
       </c>
       <c r="K18" t="n">
-        <v>0.579268</v>
+        <v>0.5962730000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5080209999999999</v>
+        <v>0.513369</v>
       </c>
       <c r="M18" t="n">
-        <v>0.541311</v>
+        <v>0.551724</v>
       </c>
       <c r="N18" t="n">
         <v>0.2</v>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_13.txt</t>
+          <t>_2_6_1_1790729834_0.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2298,7 +2298,7 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.241098</v>
+        <v>0.215825</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2315,25 +2315,25 @@
         <v>200000</v>
       </c>
       <c r="G19" t="n">
-        <v>0.551343</v>
+        <v>0.644947</v>
       </c>
       <c r="H19" t="n">
-        <v>0.440101</v>
+        <v>0.611602</v>
       </c>
       <c r="I19" t="n">
-        <v>0.489481</v>
+        <v>0.6278319999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.243971</v>
+        <v>0.217323</v>
       </c>
       <c r="K19" t="n">
-        <v>0.458333</v>
+        <v>0.618785</v>
       </c>
       <c r="L19" t="n">
-        <v>0.352941</v>
+        <v>0.59893</v>
       </c>
       <c r="M19" t="n">
-        <v>0.398792</v>
+        <v>0.608696</v>
       </c>
       <c r="N19" t="n">
         <v>0.2</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_4.txt</t>
+          <t>_2_6_1_1790729834_7.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2399,42 +2399,42 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.239717</v>
+        <v>0.218718</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1790729879</v>
+        <v>1790729834</v>
       </c>
       <c r="E20" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="F20" t="n">
         <v>200000</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5579809999999999</v>
+        <v>0.647555</v>
       </c>
       <c r="H20" t="n">
-        <v>0.515763</v>
+        <v>0.484237</v>
       </c>
       <c r="I20" t="n">
-        <v>0.536042</v>
+        <v>0.554113</v>
       </c>
       <c r="J20" t="n">
-        <v>0.245959</v>
+        <v>0.222028</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5</v>
+        <v>0.611465</v>
       </c>
       <c r="L20" t="n">
-        <v>0.470588</v>
+        <v>0.513369</v>
       </c>
       <c r="M20" t="n">
-        <v>0.484848</v>
+        <v>0.55814</v>
       </c>
       <c r="N20" t="n">
         <v>0.2</v>
@@ -2470,23 +2470,23 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_2.txt</t>
+          <t>_2_6_1_1790729834_5.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z20" t="n">
         <v>6</v>
       </c>
       <c r="AA20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2500,7 +2500,7 @@
         <v>0.1</v>
       </c>
       <c r="B21" t="n">
-        <v>0.2183</v>
+        <v>0.222821</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2517,25 +2517,25 @@
         <v>200000</v>
       </c>
       <c r="G21" t="n">
-        <v>0.647661</v>
+        <v>0.597315</v>
       </c>
       <c r="H21" t="n">
-        <v>0.558638</v>
+        <v>0.56116</v>
       </c>
       <c r="I21" t="n">
-        <v>0.599865</v>
+        <v>0.578674</v>
       </c>
       <c r="J21" t="n">
-        <v>0.221447</v>
+        <v>0.224968</v>
       </c>
       <c r="K21" t="n">
-        <v>0.59375</v>
+        <v>0.58011</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5080209999999999</v>
+        <v>0.561497</v>
       </c>
       <c r="M21" t="n">
-        <v>0.54755</v>
+        <v>0.570652</v>
       </c>
       <c r="N21" t="n">
         <v>0.2</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_14.txt</t>
+          <t>_2_6_1_1790729834_19.txt</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2601,42 +2601,42 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.227201</v>
+        <v>0.221202</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1790729879</v>
+        <v>1790729834</v>
       </c>
       <c r="E22" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
         <v>200000</v>
       </c>
       <c r="G22" t="n">
-        <v>0.57888</v>
+        <v>0.598415</v>
       </c>
       <c r="H22" t="n">
-        <v>0.57377</v>
+        <v>0.571248</v>
       </c>
       <c r="I22" t="n">
-        <v>0.576314</v>
+        <v>0.584516</v>
       </c>
       <c r="J22" t="n">
-        <v>0.230031</v>
+        <v>0.235845</v>
       </c>
       <c r="K22" t="n">
-        <v>0.512077</v>
+        <v>0.547059</v>
       </c>
       <c r="L22" t="n">
-        <v>0.566845</v>
+        <v>0.497326</v>
       </c>
       <c r="M22" t="n">
-        <v>0.538071</v>
+        <v>0.521008</v>
       </c>
       <c r="N22" t="n">
         <v>0.2</v>
@@ -2672,23 +2672,23 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_0.txt</t>
+          <t>_2_6_1_1790729834_3.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z22" t="n">
         <v>6</v>
       </c>
       <c r="AA22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2702,7 +2702,7 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.243211</v>
+        <v>0.243843</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2719,25 +2719,25 @@
         <v>200000</v>
       </c>
       <c r="G23" t="n">
-        <v>0.55267</v>
+        <v>0.552113</v>
       </c>
       <c r="H23" t="n">
-        <v>0.482976</v>
+        <v>0.247163</v>
       </c>
       <c r="I23" t="n">
-        <v>0.515478</v>
+        <v>0.341463</v>
       </c>
       <c r="J23" t="n">
-        <v>0.246204</v>
+        <v>0.24836</v>
       </c>
       <c r="K23" t="n">
-        <v>0.513514</v>
+        <v>0.460674</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5080209999999999</v>
+        <v>0.219251</v>
       </c>
       <c r="M23" t="n">
-        <v>0.510753</v>
+        <v>0.297101</v>
       </c>
       <c r="N23" t="n">
         <v>0.2</v>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_1.txt</t>
+          <t>_2_3_3_1_1790729879_4.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2803,42 +2803,42 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.222821</v>
+        <v>0.245617</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1790729834</v>
+        <v>1790729879</v>
       </c>
       <c r="E24" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="F24" t="n">
         <v>200000</v>
       </c>
       <c r="G24" t="n">
-        <v>0.597315</v>
+        <v>0.560794</v>
       </c>
       <c r="H24" t="n">
-        <v>0.56116</v>
+        <v>0.284994</v>
       </c>
       <c r="I24" t="n">
-        <v>0.578674</v>
+        <v>0.377926</v>
       </c>
       <c r="J24" t="n">
-        <v>0.224968</v>
+        <v>0.250612</v>
       </c>
       <c r="K24" t="n">
-        <v>0.58011</v>
+        <v>0.480392</v>
       </c>
       <c r="L24" t="n">
-        <v>0.561497</v>
+        <v>0.262032</v>
       </c>
       <c r="M24" t="n">
-        <v>0.570652</v>
+        <v>0.3391</v>
       </c>
       <c r="N24" t="n">
         <v>0.2</v>
@@ -2874,23 +2874,23 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_19.txt</t>
+          <t>_2_3_3_1_1790729879_6.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z24" t="n">
         <v>6</v>
       </c>
       <c r="AA24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -2904,42 +2904,42 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.225568</v>
+        <v>0.218277</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1790729879</v>
+        <v>1790729834</v>
       </c>
       <c r="E25" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="F25" t="n">
         <v>200000</v>
       </c>
       <c r="G25" t="n">
-        <v>0.580071</v>
+        <v>0.626591</v>
       </c>
       <c r="H25" t="n">
-        <v>0.411097</v>
+        <v>0.558638</v>
       </c>
       <c r="I25" t="n">
-        <v>0.481181</v>
+        <v>0.5906670000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>0.229596</v>
+        <v>0.21852</v>
       </c>
       <c r="K25" t="n">
-        <v>0.564516</v>
+        <v>0.666667</v>
       </c>
       <c r="L25" t="n">
-        <v>0.374332</v>
+        <v>0.55615</v>
       </c>
       <c r="M25" t="n">
-        <v>0.450161</v>
+        <v>0.606414</v>
       </c>
       <c r="N25" t="n">
         <v>0.2</v>
@@ -2975,23 +2975,23 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_7.txt</t>
+          <t>_2_6_1_1790729834_8.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z25" t="n">
         <v>6</v>
       </c>
       <c r="AA25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3005,42 +3005,42 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.223623</v>
+        <v>0.239717</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1790729834</v>
+        <v>1790729879</v>
       </c>
       <c r="E26" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="F26" t="n">
         <v>200000</v>
       </c>
       <c r="G26" t="n">
-        <v>0.589641</v>
+        <v>0.5579809999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>0.559899</v>
+        <v>0.515763</v>
       </c>
       <c r="I26" t="n">
-        <v>0.574386</v>
+        <v>0.536042</v>
       </c>
       <c r="J26" t="n">
-        <v>0.225489</v>
+        <v>0.245959</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="L26" t="n">
-        <v>0.529412</v>
+        <v>0.470588</v>
       </c>
       <c r="M26" t="n">
-        <v>0.545455</v>
+        <v>0.484848</v>
       </c>
       <c r="N26" t="n">
         <v>0.2</v>
@@ -3076,23 +3076,23 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_17.txt</t>
+          <t>_2_3_3_1_1790729879_2.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z26" t="n">
         <v>6</v>
       </c>
       <c r="AA26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3106,7 +3106,7 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.248883</v>
+        <v>0.226249</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3123,25 +3123,25 @@
         <v>200000</v>
       </c>
       <c r="G27" t="n">
-        <v>0.527512</v>
+        <v>0.575</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5561160000000001</v>
+        <v>0.580076</v>
       </c>
       <c r="I27" t="n">
-        <v>0.541436</v>
+        <v>0.577527</v>
       </c>
       <c r="J27" t="n">
-        <v>0.251582</v>
+        <v>0.2284</v>
       </c>
       <c r="K27" t="n">
-        <v>0.464789</v>
+        <v>0.518519</v>
       </c>
       <c r="L27" t="n">
-        <v>0.529412</v>
+        <v>0.59893</v>
       </c>
       <c r="M27" t="n">
-        <v>0.495</v>
+        <v>0.555831</v>
       </c>
       <c r="N27" t="n">
         <v>0.2</v>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_5.txt</t>
+          <t>_2_3_3_1_1790729879_18.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3207,7 +3207,7 @@
         <v>0.1</v>
       </c>
       <c r="B28" t="n">
-        <v>0.218277</v>
+        <v>0.2183</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3224,25 +3224,25 @@
         <v>200000</v>
       </c>
       <c r="G28" t="n">
-        <v>0.626591</v>
+        <v>0.647661</v>
       </c>
       <c r="H28" t="n">
         <v>0.558638</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5906670000000001</v>
+        <v>0.599865</v>
       </c>
       <c r="J28" t="n">
-        <v>0.21852</v>
+        <v>0.221447</v>
       </c>
       <c r="K28" t="n">
-        <v>0.666667</v>
+        <v>0.59375</v>
       </c>
       <c r="L28" t="n">
-        <v>0.55615</v>
+        <v>0.5080209999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>0.606414</v>
+        <v>0.54755</v>
       </c>
       <c r="N28" t="n">
         <v>0.2</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_8.txt</t>
+          <t>_2_6_1_1790729834_14.txt</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3308,7 +3308,7 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.216577</v>
+        <v>0.215203</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3325,25 +3325,25 @@
         <v>200000</v>
       </c>
       <c r="G29" t="n">
-        <v>0.624152</v>
+        <v>0.609524</v>
       </c>
       <c r="H29" t="n">
-        <v>0.580076</v>
+        <v>0.645649</v>
       </c>
       <c r="I29" t="n">
-        <v>0.601307</v>
+        <v>0.627067</v>
       </c>
       <c r="J29" t="n">
-        <v>0.219792</v>
+        <v>0.217863</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5820109999999999</v>
+        <v>0.566667</v>
       </c>
       <c r="L29" t="n">
-        <v>0.588235</v>
+        <v>0.636364</v>
       </c>
       <c r="M29" t="n">
-        <v>0.585106</v>
+        <v>0.599496</v>
       </c>
       <c r="N29" t="n">
         <v>0.2</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_18.txt</t>
+          <t>_2_6_1_1790729834_11.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3409,7 +3409,7 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.23057</v>
+        <v>0.218953</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3426,25 +3426,25 @@
         <v>200000</v>
       </c>
       <c r="G30" t="n">
-        <v>0.60503</v>
+        <v>0.649371</v>
       </c>
       <c r="H30" t="n">
-        <v>0.515763</v>
+        <v>0.520807</v>
       </c>
       <c r="I30" t="n">
-        <v>0.556841</v>
+        <v>0.578027</v>
       </c>
       <c r="J30" t="n">
-        <v>0.243836</v>
+        <v>0.221643</v>
       </c>
       <c r="K30" t="n">
-        <v>0.489933</v>
+        <v>0.608696</v>
       </c>
       <c r="L30" t="n">
-        <v>0.390374</v>
+        <v>0.524064</v>
       </c>
       <c r="M30" t="n">
-        <v>0.434524</v>
+        <v>0.563218</v>
       </c>
       <c r="N30" t="n">
         <v>0.2</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_1.txt</t>
+          <t>_2_6_1_1790729834_10.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3510,7 +3510,7 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.248769</v>
+        <v>0.248748</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3527,25 +3527,25 @@
         <v>200000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.534247</v>
+        <v>0.5286459999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>0.491803</v>
+        <v>0.51198</v>
       </c>
       <c r="I31" t="n">
-        <v>0.512147</v>
+        <v>0.5201789999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>0.252621</v>
+        <v>0.252082</v>
       </c>
       <c r="K31" t="n">
-        <v>0.433155</v>
+        <v>0.439394</v>
       </c>
       <c r="L31" t="n">
-        <v>0.433155</v>
+        <v>0.465241</v>
       </c>
       <c r="M31" t="n">
-        <v>0.433155</v>
+        <v>0.451948</v>
       </c>
       <c r="N31" t="n">
         <v>0.2</v>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_8.txt</t>
+          <t>_2_3_3_1_1790729879_16.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3611,42 +3611,42 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.247946</v>
+        <v>0.219263</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>_2_3_3_1_</t>
+          <t>_2_6_1_</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1790729879</v>
+        <v>1790729834</v>
       </c>
       <c r="E32" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="F32" t="n">
         <v>200000</v>
       </c>
       <c r="G32" t="n">
-        <v>0.515537</v>
+        <v>0.6411480000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.460277</v>
+        <v>0.5069360000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>0.486342</v>
+        <v>0.566197</v>
       </c>
       <c r="J32" t="n">
-        <v>0.250513</v>
+        <v>0.221056</v>
       </c>
       <c r="K32" t="n">
-        <v>0.446328</v>
+        <v>0.615385</v>
       </c>
       <c r="L32" t="n">
-        <v>0.42246</v>
+        <v>0.513369</v>
       </c>
       <c r="M32" t="n">
-        <v>0.434066</v>
+        <v>0.559767</v>
       </c>
       <c r="N32" t="n">
         <v>0.2</v>
@@ -3682,23 +3682,23 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_19.txt</t>
+          <t>_2_6_1_1790729834_12.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>[3, 3]</t>
+          <t>[6]</t>
         </is>
       </c>
       <c r="Z32" t="n">
         <v>6</v>
       </c>
       <c r="AA32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3712,42 +3712,42 @@
         <v>0.1</v>
       </c>
       <c r="B33" t="n">
-        <v>0.239137</v>
+        <v>0.248498</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1790729834</v>
+        <v>1790729879</v>
       </c>
       <c r="E33" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="F33" t="n">
         <v>200000</v>
       </c>
       <c r="G33" t="n">
-        <v>0.546995</v>
+        <v>0.553468</v>
       </c>
       <c r="H33" t="n">
-        <v>0.447667</v>
+        <v>0.482976</v>
       </c>
       <c r="I33" t="n">
-        <v>0.492372</v>
+        <v>0.515825</v>
       </c>
       <c r="J33" t="n">
-        <v>0.242724</v>
+        <v>0.251417</v>
       </c>
       <c r="K33" t="n">
-        <v>0.503401</v>
+        <v>0.505952</v>
       </c>
       <c r="L33" t="n">
-        <v>0.395722</v>
+        <v>0.454545</v>
       </c>
       <c r="M33" t="n">
-        <v>0.443114</v>
+        <v>0.478873</v>
       </c>
       <c r="N33" t="n">
         <v>0.2</v>
@@ -3783,23 +3783,23 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_9.txt</t>
+          <t>_2_3_3_1_1790729879_10.txt</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z33" t="n">
         <v>6</v>
       </c>
       <c r="AA33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -3813,7 +3813,7 @@
         <v>0.1</v>
       </c>
       <c r="B34" t="n">
-        <v>0.245234</v>
+        <v>0.234669</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3830,25 +3830,25 @@
         <v>200000</v>
       </c>
       <c r="G34" t="n">
-        <v>0.535664</v>
+        <v>0.544811</v>
       </c>
       <c r="H34" t="n">
-        <v>0.482976</v>
+        <v>0.291299</v>
       </c>
       <c r="I34" t="n">
-        <v>0.507958</v>
+        <v>0.379622</v>
       </c>
       <c r="J34" t="n">
-        <v>0.251466</v>
+        <v>0.238642</v>
       </c>
       <c r="K34" t="n">
-        <v>0.478261</v>
+        <v>0.524272</v>
       </c>
       <c r="L34" t="n">
-        <v>0.470588</v>
+        <v>0.28877</v>
       </c>
       <c r="M34" t="n">
-        <v>0.474394</v>
+        <v>0.372414</v>
       </c>
       <c r="N34" t="n">
         <v>0.2</v>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_12.txt</t>
+          <t>_2_3_3_1_1790729879_3.txt</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3914,7 +3914,7 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.218718</v>
+        <v>0.216577</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3931,25 +3931,25 @@
         <v>200000</v>
       </c>
       <c r="G35" t="n">
-        <v>0.647555</v>
+        <v>0.624152</v>
       </c>
       <c r="H35" t="n">
-        <v>0.484237</v>
+        <v>0.580076</v>
       </c>
       <c r="I35" t="n">
-        <v>0.554113</v>
+        <v>0.601307</v>
       </c>
       <c r="J35" t="n">
-        <v>0.222028</v>
+        <v>0.219792</v>
       </c>
       <c r="K35" t="n">
-        <v>0.611465</v>
+        <v>0.5820109999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>0.513369</v>
+        <v>0.588235</v>
       </c>
       <c r="M35" t="n">
-        <v>0.55814</v>
+        <v>0.585106</v>
       </c>
       <c r="N35" t="n">
         <v>0.2</v>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_5.txt</t>
+          <t>_2_6_1_1790729834_18.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4015,7 +4015,7 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.248651</v>
+        <v>0.227201</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4032,25 +4032,25 @@
         <v>200000</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5074419999999999</v>
+        <v>0.57888</v>
       </c>
       <c r="H36" t="n">
-        <v>0.472888</v>
+        <v>0.57377</v>
       </c>
       <c r="I36" t="n">
-        <v>0.489556</v>
+        <v>0.576314</v>
       </c>
       <c r="J36" t="n">
-        <v>0.2527</v>
+        <v>0.230031</v>
       </c>
       <c r="K36" t="n">
-        <v>0.444444</v>
+        <v>0.512077</v>
       </c>
       <c r="L36" t="n">
-        <v>0.427807</v>
+        <v>0.566845</v>
       </c>
       <c r="M36" t="n">
-        <v>0.435967</v>
+        <v>0.538071</v>
       </c>
       <c r="N36" t="n">
         <v>0.2</v>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_17.txt</t>
+          <t>_2_3_3_1_1790729879_0.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4116,7 +4116,7 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.226233</v>
+        <v>0.243211</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4133,25 +4133,25 @@
         <v>200000</v>
       </c>
       <c r="G37" t="n">
-        <v>0.577256</v>
+        <v>0.55267</v>
       </c>
       <c r="H37" t="n">
-        <v>0.588903</v>
+        <v>0.482976</v>
       </c>
       <c r="I37" t="n">
-        <v>0.583021</v>
+        <v>0.515478</v>
       </c>
       <c r="J37" t="n">
-        <v>0.228458</v>
+        <v>0.246204</v>
       </c>
       <c r="K37" t="n">
-        <v>0.514286</v>
+        <v>0.513514</v>
       </c>
       <c r="L37" t="n">
-        <v>0.5775400000000001</v>
+        <v>0.5080209999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>0.544081</v>
+        <v>0.510753</v>
       </c>
       <c r="N37" t="n">
         <v>0.2</v>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_15.txt</t>
+          <t>_2_3_3_1_1790729879_1.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4217,7 +4217,7 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.226249</v>
+        <v>0.247946</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4234,25 +4234,25 @@
         <v>200000</v>
       </c>
       <c r="G38" t="n">
-        <v>0.575</v>
+        <v>0.515537</v>
       </c>
       <c r="H38" t="n">
-        <v>0.580076</v>
+        <v>0.460277</v>
       </c>
       <c r="I38" t="n">
-        <v>0.577527</v>
+        <v>0.486342</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2284</v>
+        <v>0.250513</v>
       </c>
       <c r="K38" t="n">
-        <v>0.518519</v>
+        <v>0.446328</v>
       </c>
       <c r="L38" t="n">
-        <v>0.59893</v>
+        <v>0.42246</v>
       </c>
       <c r="M38" t="n">
-        <v>0.555831</v>
+        <v>0.434066</v>
       </c>
       <c r="N38" t="n">
         <v>0.2</v>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_18.txt</t>
+          <t>_2_3_3_1_1790729879_19.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4318,42 +4318,42 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.214512</v>
+        <v>0.247883</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>_2_6_1_</t>
+          <t>_2_3_3_1_</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1790729834</v>
+        <v>1790729879</v>
       </c>
       <c r="E39" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="F39" t="n">
         <v>200000</v>
       </c>
       <c r="G39" t="n">
-        <v>0.633152</v>
+        <v>0.535433</v>
       </c>
       <c r="H39" t="n">
-        <v>0.587642</v>
+        <v>0.428752</v>
       </c>
       <c r="I39" t="n">
-        <v>0.609549</v>
+        <v>0.47619</v>
       </c>
       <c r="J39" t="n">
-        <v>0.216096</v>
+        <v>0.251054</v>
       </c>
       <c r="K39" t="n">
-        <v>0.596591</v>
+        <v>0.432258</v>
       </c>
       <c r="L39" t="n">
-        <v>0.561497</v>
+        <v>0.358289</v>
       </c>
       <c r="M39" t="n">
-        <v>0.578512</v>
+        <v>0.391813</v>
       </c>
       <c r="N39" t="n">
         <v>0.2</v>
@@ -4389,23 +4389,23 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_6.txt</t>
+          <t>_2_3_3_1_1790729879_11.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>[6]</t>
+          <t>[3, 3]</t>
         </is>
       </c>
       <c r="Z39" t="n">
         <v>6</v>
       </c>
       <c r="AA39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4419,7 +4419,7 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.221202</v>
+        <v>0.216022</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4436,25 +4436,25 @@
         <v>200000</v>
       </c>
       <c r="G40" t="n">
-        <v>0.598415</v>
+        <v>0.613609</v>
       </c>
       <c r="H40" t="n">
-        <v>0.571248</v>
+        <v>0.636822</v>
       </c>
       <c r="I40" t="n">
-        <v>0.584516</v>
+        <v>0.625</v>
       </c>
       <c r="J40" t="n">
-        <v>0.235845</v>
+        <v>0.218002</v>
       </c>
       <c r="K40" t="n">
-        <v>0.547059</v>
+        <v>0.576355</v>
       </c>
       <c r="L40" t="n">
-        <v>0.497326</v>
+        <v>0.625668</v>
       </c>
       <c r="M40" t="n">
-        <v>0.521008</v>
+        <v>0.6</v>
       </c>
       <c r="N40" t="n">
         <v>0.2</v>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_2_6_1_1790729834_3.txt</t>
+          <t>_2_6_1_1790729834_16.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -4520,7 +4520,7 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.248484</v>
+        <v>0.248651</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4537,25 +4537,25 @@
         <v>200000</v>
       </c>
       <c r="G41" t="n">
-        <v>0.537037</v>
+        <v>0.5074419999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>0.43884</v>
+        <v>0.472888</v>
       </c>
       <c r="I41" t="n">
-        <v>0.482998</v>
+        <v>0.489556</v>
       </c>
       <c r="J41" t="n">
-        <v>0.252834</v>
+        <v>0.2527</v>
       </c>
       <c r="K41" t="n">
-        <v>0.460606</v>
+        <v>0.444444</v>
       </c>
       <c r="L41" t="n">
-        <v>0.406417</v>
+        <v>0.427807</v>
       </c>
       <c r="M41" t="n">
-        <v>0.431818</v>
+        <v>0.435967</v>
       </c>
       <c r="N41" t="n">
         <v>0.2</v>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_2_3_3_1_1790729879_14.txt</t>
+          <t>_2_3_3_1_1790729879_17.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -4710,7 +4710,7 @@
         <v>0.5506306000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05979010934259946</v>
+        <v>0.05979010934259955</v>
       </c>
       <c r="D3" t="n">
         <v>0.608696</v>
